--- a/data/performance/daily/signal_list_2026-05-08.xlsx
+++ b/data/performance/daily/signal_list_2026-05-08.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 34.3%  (46W / 88L of 134 evaluated)</t>
+          <t>Win Rate: 38.1%  (51W / 83L of 134 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D8" t="n">
         <v>408</v>
@@ -679,10 +679,10 @@
         <v>412</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="D9" t="n">
         <v>1590</v>
@@ -721,10 +721,10 @@
         <v>1800</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.09</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="D11" t="n">
         <v>950</v>
@@ -805,10 +805,10 @@
         <v>1000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-5</v>
+        <v>-4.52</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>76</v>
@@ -973,10 +973,10 @@
         <v>79</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4660</v>
+        <v>4510</v>
       </c>
       <c r="D16" t="n">
         <v>4700</v>
@@ -1015,10 +1015,10 @@
         <v>4830</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.65</v>
+        <v>7.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.86</v>
+        <v>4.21</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="D19" t="n">
         <v>1660</v>
@@ -1141,10 +1141,10 @@
         <v>1700</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.06</v>
+        <v>-1.78</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="D22" t="n">
         <v>2350</v>
@@ -1267,10 +1267,10 @@
         <v>2410</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D23" t="n">
         <v>350</v>
@@ -1309,14 +1309,14 @@
         <v>354</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.57</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D33" t="n">
         <v>1240</v>
@@ -1729,10 +1729,10 @@
         <v>1245</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D34" t="n">
         <v>140</v>
@@ -1771,10 +1771,10 @@
         <v>147</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.08</v>
+        <v>4.26</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.78</v>
+        <v>-0.71</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D37" t="n">
         <v>188</v>
@@ -1897,10 +1897,10 @@
         <v>198</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.51</v>
+        <v>1.54</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-4.57</v>
+        <v>-3.59</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6950</v>
+        <v>6975</v>
       </c>
       <c r="D39" t="n">
         <v>6925</v>
@@ -1981,10 +1981,10 @@
         <v>7000</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="D40" t="n">
         <v>3160</v>
@@ -2023,10 +2023,10 @@
         <v>3500</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.41</v>
+        <v>10.76</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D41" t="n">
         <v>125</v>
@@ -2065,10 +2065,10 @@
         <v>129</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-1.57</v>
+        <v>-0.79</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" t="n">
         <v>160</v>
@@ -2107,10 +2107,10 @@
         <v>160</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2410</v>
+        <v>2550</v>
       </c>
       <c r="D44" t="n">
         <v>2530</v>
@@ -2191,14 +2191,14 @@
         <v>2530</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4.98</v>
+        <v>-0.78</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.78</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D45" t="n">
         <v>180</v>
@@ -2233,10 +2233,10 @@
         <v>186</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-1.1</v>
+        <v>-2.7</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D46" t="n">
         <v>434</v>
@@ -2275,10 +2275,10 @@
         <v>440</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1.36</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D47" t="n">
         <v>118</v>
@@ -2317,10 +2317,10 @@
         <v>131</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3.97</v>
+        <v>0.77</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-6.35</v>
+        <v>-9.23</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4250</v>
+        <v>4270</v>
       </c>
       <c r="D48" t="n">
         <v>4280</v>
@@ -2359,10 +2359,10 @@
         <v>4380</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3.06</v>
+        <v>2.58</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D51" t="n">
         <v>204</v>
@@ -2485,14 +2485,14 @@
         <v>250</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>20.19</v>
+        <v>25</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D52" t="n">
         <v>127</v>
@@ -2527,10 +2527,10 @@
         <v>133</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>15.65</v>
+        <v>19.82</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>10.43</v>
+        <v>14.41</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3130</v>
+        <v>3150</v>
       </c>
       <c r="D53" t="n">
         <v>3060</v>
@@ -2569,10 +2569,10 @@
         <v>3150</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-2.24</v>
+        <v>-2.86</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D54" t="n">
         <v>73</v>
@@ -2611,10 +2611,10 @@
         <v>79</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-7.59</v>
+        <v>-2.67</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
         <v>101</v>
@@ -2653,14 +2653,14 @@
         <v>105</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D56" t="n">
         <v>258</v>
@@ -2695,10 +2695,10 @@
         <v>270</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-4.44</v>
+        <v>-3.01</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6200</v>
+        <v>6125</v>
       </c>
       <c r="D57" t="n">
         <v>6225</v>
@@ -2737,10 +2737,10 @@
         <v>6225</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.4</v>
+        <v>1.63</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0.4</v>
+        <v>1.63</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="D59" t="n">
         <v>760</v>
@@ -2821,10 +2821,10 @@
         <v>1000</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>16.28</v>
+        <v>12.36</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-11.63</v>
+        <v>-14.61</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="D60" t="n">
         <v>1330</v>
@@ -2863,10 +2863,10 @@
         <v>1345</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.37</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3380</v>
+        <v>3490</v>
       </c>
       <c r="D61" t="n">
         <v>3560</v>
@@ -2905,10 +2905,10 @@
         <v>3900</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>15.38</v>
+        <v>11.75</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5.33</v>
+        <v>2.01</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="D62" t="n">
         <v>1230</v>
@@ -2947,10 +2947,10 @@
         <v>1250</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="D63" t="n">
         <v>1600</v>
@@ -2989,10 +2989,10 @@
         <v>1625</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.31</v>
+        <v>1.56</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-1.23</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D66" t="n">
         <v>396</v>
@@ -3115,10 +3115,10 @@
         <v>412</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2550</v>
+        <v>2530</v>
       </c>
       <c r="D68" t="n">
         <v>2600</v>
@@ -3199,10 +3199,10 @@
         <v>2900</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>13.73</v>
+        <v>14.62</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="D69" t="n">
         <v>850</v>
@@ -3241,14 +3241,14 @@
         <v>885</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3.51</v>
+        <v>5.36</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.19</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D70" t="n">
         <v>550</v>
@@ -3283,14 +3283,14 @@
         <v>555</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.92</v>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" t="n">
         <v>83</v>
@@ -3451,10 +3451,10 @@
         <v>86</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-3.49</v>
+        <v>-2.35</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8575</v>
+        <v>8600</v>
       </c>
       <c r="D76" t="n">
         <v>8700</v>
@@ -3535,10 +3535,10 @@
         <v>8750</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D78" t="n">
         <v>162</v>
@@ -3619,10 +3619,10 @@
         <v>171</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>7.55</v>
+        <v>6.88</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D83" t="n">
         <v>83</v>
@@ -3829,10 +3829,10 @@
         <v>85</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>-2.35</v>
+        <v>-3.49</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D85" t="n">
         <v>50</v>
@@ -3913,10 +3913,10 @@
         <v>55</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>-9.09</v>
+        <v>-5.66</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D87" t="n">
         <v>81</v>
@@ -3997,14 +3997,14 @@
         <v>81</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.25</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2400</v>
+        <v>2360</v>
       </c>
       <c r="D88" t="n">
         <v>2330</v>
@@ -4039,10 +4039,10 @@
         <v>2600</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>8.33</v>
+        <v>10.17</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-2.92</v>
+        <v>-1.27</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -4081,10 +4081,10 @@
         <v>101</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>16.09</v>
+        <v>17.44</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>1.15</v>
+        <v>2.33</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D90" t="n">
         <v>560</v>
@@ -4123,10 +4123,10 @@
         <v>595</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-5.88</v>
+        <v>-6.67</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D92" t="n">
         <v>75</v>
@@ -4207,10 +4207,10 @@
         <v>78</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D93" t="n">
         <v>168</v>
@@ -4249,10 +4249,10 @@
         <v>174</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>3.57</v>
+        <v>2.35</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D94" t="n">
         <v>1080</v>
@@ -4291,10 +4291,10 @@
         <v>1155</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.43</v>
+        <v>-3.75</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-6.09</v>
+        <v>-10</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D95" t="n">
         <v>810</v>
@@ -4333,10 +4333,10 @@
         <v>815</v>
       </c>
       <c r="F95" s="4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G95" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v>-0.61</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D97" t="n">
         <v>294</v>
@@ -4417,10 +4417,10 @@
         <v>320</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>11.11</v>
+        <v>11.89</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D99" t="n">
         <v>95</v>
@@ -4501,14 +4501,14 @@
         <v>101</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>5.21</v>
+        <v>8.6</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.15</v>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D102" t="n">
         <v>82</v>
@@ -4627,10 +4627,10 @@
         <v>83</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>7.79</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>6.49</v>
+        <v>7.89</v>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D103" t="n">
         <v>426</v>
@@ -4669,10 +4669,10 @@
         <v>434</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>5.34</v>
+        <v>6.37</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>3.4</v>
+        <v>4.41</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D104" t="n">
         <v>48</v>
@@ -4711,14 +4711,14 @@
         <v>48</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9.09</v>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D105" t="n">
         <v>78</v>
@@ -4753,10 +4753,10 @@
         <v>84</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>6.33</v>
+        <v>3.7</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>-1.27</v>
+        <v>-3.7</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D106" t="n">
         <v>138</v>
@@ -4795,10 +4795,10 @@
         <v>157</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>24.6</v>
+        <v>34.19</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>9.52</v>
+        <v>17.95</v>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D107" t="n">
         <v>126</v>
@@ -4837,10 +4837,10 @@
         <v>132</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2.33</v>
+        <v>0.76</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>-2.33</v>
+        <v>-3.82</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D108" t="n">
         <v>360</v>
@@ -4879,10 +4879,10 @@
         <v>390</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D109" t="n">
         <v>169</v>
@@ -4921,14 +4921,14 @@
         <v>175</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>4.17</v>
+        <v>2.94</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.59</v>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="D110" t="n">
         <v>1015</v>
@@ -4963,10 +4963,10 @@
         <v>1035</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>9.52</v>
+        <v>10.11</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>7.41</v>
+        <v>7.98</v>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D112" t="n">
         <v>97</v>
@@ -5047,10 +5047,10 @@
         <v>104</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>6.59</v>
+        <v>10.23</v>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D113" t="n">
         <v>448</v>
@@ -5089,10 +5089,10 @@
         <v>452</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>4.15</v>
+        <v>3.67</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="D114" t="n">
         <v>995</v>
@@ -5131,10 +5131,10 @@
         <v>1010</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D118" t="n">
         <v>396</v>
@@ -5299,10 +5299,10 @@
         <v>420</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>8.25</v>
+        <v>8.81</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2.06</v>
+        <v>2.59</v>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D119" t="n">
         <v>95</v>
@@ -5341,10 +5341,10 @@
         <v>98</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>4.26</v>
+        <v>5.38</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1.06</v>
+        <v>2.15</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D121" t="n">
         <v>94</v>
@@ -5425,10 +5425,10 @@
         <v>100</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>16.28</v>
+        <v>19.05</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D122" t="n">
         <v>67</v>
@@ -5467,10 +5467,10 @@
         <v>68</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>6.25</v>
+        <v>4.62</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>4.69</v>
+        <v>3.08</v>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="D125" t="n">
         <v>510</v>
@@ -5593,10 +5593,10 @@
         <v>530</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>4.95</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>0.99</v>
+        <v>4.51</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D127" t="n">
         <v>121</v>
@@ -5677,10 +5677,10 @@
         <v>130</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1.56</v>
+        <v>3.17</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>-5.47</v>
+        <v>-3.97</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D130" t="n">
         <v>89</v>
@@ -5803,10 +5803,10 @@
         <v>98</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>18.07</v>
+        <v>22.5</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>7.23</v>
+        <v>11.25</v>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="D131" t="n">
         <v>498</v>
@@ -5845,10 +5845,10 @@
         <v>570</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>16.33</v>
+        <v>22.32</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1.63</v>
+        <v>6.87</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D132" t="n">
         <v>134</v>
@@ -5887,14 +5887,14 @@
         <v>140</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4.29</v>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D133" t="n">
         <v>177</v>
@@ -5929,10 +5929,10 @@
         <v>192</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>10.34</v>
+        <v>11.63</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="D134" t="n">
         <v>515</v>
@@ -5971,10 +5971,10 @@
         <v>519.86</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7100</v>
+        <v>7050</v>
       </c>
       <c r="D135" t="n">
         <v>7100</v>
@@ -6013,14 +6013,14 @@
         <v>7100</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.71</v>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D136" t="n">
         <v>153</v>
@@ -6055,14 +6055,14 @@
         <v>155</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1.97</v>
+        <v>-0.64</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.92</v>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
